--- a/outputs/sample_close_pack/sample_close_pack.xlsx
+++ b/outputs/sample_close_pack/sample_close_pack.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-16 17:06:07 UTC</t>
+          <t>2026-06-16 19:37:26 UTC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/outputs/sample_close_pack/sample_close_pack.xlsx
+++ b/outputs/sample_close_pack/sample_close_pack.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-16 19:37:26 UTC</t>
+          <t>2026-06-16 19:55:35 UTC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
